--- a/budget_to_actual_bridge.xlsx
+++ b/budget_to_actual_bridge.xlsx
@@ -5,17 +5,19 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="Account Bridge" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Account Bridge Budget vs Actual" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Revenue Bridge" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="RnM Bridge" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Inbound Freight Bridge" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Raw Materials Bridge" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Direct Labor – Regular Bridge" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Direct Labor – Overtime Bridge" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Event Bridge" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Event Bridge Budget vs Actual" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Event Bridge Budget vs Forecast" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Event Bridge Forecast vs Actual" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="46">
   <si>
     <t xml:space="preserve">CategoryKey</t>
   </si>
@@ -162,6 +164,9 @@
   </si>
   <si>
     <t xml:space="preserve">Impact of Normal Fluctuations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast</t>
   </si>
 </sst>
 </file>
@@ -482,6 +487,85 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="47.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="38.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -756,7 +840,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="23.94"/>
@@ -838,9 +922,6 @@
       <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1152,4 +1233,138 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="47.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="38.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>